--- a/shucle_report/영덕관광/20260101_20260228/report_영덕관광_20260101_20260228.xlsx
+++ b/shucle_report/영덕관광/20260101_20260228/report_영덕관광_20260101_20260228.xlsx
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>분석기간: 2026.01.01 ~ 02.28 | 생성: 2026-03-26 13:46 | 차트: 116개</t>
+          <t>분석기간: 2026.01.01 ~ 02.28 | 생성: 2026-03-26 14:48 | 차트: 116개</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>3.0건</t>
+          <t>1.8건</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>2.6건</t>
+          <t>1.4건</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>4.1명</t>
+          <t>2.2명</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>5.4분</t>
+          <t>2.2분</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>1.1배</t>
+          <t>0.4배</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>23.0분</t>
+          <t>9.4분</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>1.7명</t>
+          <t>0.8명</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>1.6명</t>
+          <t>0.6명</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
@@ -1101,21 +1101,21 @@
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>• 수요 현황: 일평균 호출 3.0건, 이동완료 2.6건, 탑승객 4.1명</t>
+          <t>• 수요 현황: 일평균 호출 1.8건, 이동완료 1.4건, 탑승객 2.2명</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>• 대기시간 현황: 평균 5.4분</t>
+          <t>• 대기시간 현황: 평균 2.2분</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>• 가호출 성공률 현황: 6.7%</t>
+          <t>• 가호출 성공률 현황: 3.3%</t>
         </is>
       </c>
     </row>
